--- a/results/link-prediction-gcn/Link/0shot/PubMed/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/0shot/PubMed/GCN_total_results.xlsx
@@ -903,447 +903,447 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>0.4337±0.0130</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.4788±0.0386</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4251±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5030±0.0043</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5096±0.0068</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5096±0.0068</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5096±0.0068</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5214±0.0302</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.7341±0.0010</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.7272±0.0105</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5144±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5144±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5144±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4704±0.0138</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.4575±0.0099</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.4961±0.0014</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.4974±0.0016</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5798±0.1129</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5535±0.0026</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5535±0.0026</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5535±0.0026</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5784±0.1109</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.7348±0.0023</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5554±0.0029</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.6101±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.6740±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4751±0.0305</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5382±0.0306</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4352±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4299±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.4975±0.0000</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5742±0.0147</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.7495±0.0026</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.7495±0.0026</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.7495±0.0026</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.6496±0.0443</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.7324±0.0060</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.7485±0.0045</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5341±0.0192</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4880±0.0063</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5279±0.0505</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.7503±0.0039</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.7459±0.0034</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.7459±0.0034</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7459±0.0034</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.7489±0.0043</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.7097±0.0007</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7512±0.0065</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.4886±0.0161</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5008±0.0007</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4497±0.0357</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.4945±0.0026</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.5237±0.0335</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5049±0.0026</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5955±0.0022</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5955±0.0022</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5955±0.0022</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5021±0.0014</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7175±0.0039</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.7365±0.0063</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4970±0.0019</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.4942±0.0047</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4532±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4993±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5301±0.0426</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5209±0.0295</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.6621±0.0937</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.7260±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.7260±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.7260±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.7218±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.7426±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4944±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4713±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4934±0.0178</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.4829±0.0350</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.7260±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.6983±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.6983±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.6983±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.7285±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.7095±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.6911±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.4429±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5002±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4663±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.5002±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5025±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5978±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5978±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5978±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5010±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.7215±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.7113±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4985±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.4945±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5298±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4922±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4909±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5131±0.0000</t>
+          <t>0.5081±0.0041</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5039±0.0000</t>
+          <t>0.5100±0.0008</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5039±0.0000</t>
+          <t>0.5100±0.0008</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5039±0.0000</t>
+          <t>0.5100±0.0008</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5196±0.0069</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5366±0.0000</t>
+          <t>0.5466±0.0192</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5096±0.0000</t>
+          <t>0.5246±0.0017</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.4444±0.3143</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1365,447 +1365,447 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>0.5949±0.0162</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6192±0.0374</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.5754±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6680±0.0019</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6710±0.0030</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6710±0.0030</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6710±0.0030</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6765±0.0139</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.7805±0.0007</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.7799±0.0067</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.6731±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.6731±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.6731±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6017±0.0046</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5961±0.0094</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6578±0.0048</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6633±0.0025</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7071±0.0572</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6912±0.0012</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6912±0.0012</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6912±0.0012</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7062±0.0559</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7852±0.0020</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6922±0.0014</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6733±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7413±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6346±0.0393</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6730±0.0158</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.5678±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.5707±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.6611±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.7012±0.0072</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7965±0.0018</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7965±0.0018</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7965±0.0018</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.7393±0.0228</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7820±0.0046</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.7960±0.0031</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6823±0.0088</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6496±0.0047</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6652±0.0243</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7965±0.0024</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7941±0.0021</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7941±0.0021</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7941±0.0021</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7957±0.0027</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7640±0.0006</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7974±0.0042</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.4328±0.3064</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6670±0.0003</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6111±0.0400</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6572±0.0019</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6777±0.0156</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6688±0.0012</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7119±0.0012</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7119±0.0012</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7119±0.0012</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6676±0.0006</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7744±0.0027</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7852±0.0043</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.4444±0.3143</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6620±0.0043</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6593±0.0068</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6809±0.0201</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6052±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6653±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6763±0.0137</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.7445±0.0458</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7815±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7815±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7815±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.7741±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.7916±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6664±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6355±0.0097</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6085±0.0298</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6584±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6240±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6668±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7755±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7627±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7627±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7627±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7777±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7624±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7578±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6036±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6668±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6342±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6678±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.7131±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.7131±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.7131±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6671±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7775±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7709±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6559±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6616±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6801±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6556±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.6565±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6720±0.0000</t>
+          <t>0.6700±0.0016</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6678±0.0000</t>
+          <t>0.6696±0.0003</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6678±0.0000</t>
+          <t>0.6696±0.0003</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6678±0.0000</t>
+          <t>0.6696±0.0003</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6727±0.0000</t>
+          <t>0.6746±0.0029</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6814±0.0000</t>
+          <t>0.6865±0.0082</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6706±0.0000</t>
+          <t>0.6766±0.0007</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8174±0.0000</t>
+          <t>0.7338±0.0944</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8996±0.0000</t>
+          <t>0.8996±0.0015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5745±0.0000</t>
+          <t>0.6752±0.0087</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6727±0.0000</t>
+          <t>0.7361±0.0622</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.9144±0.0000</t>
+          <t>0.8992±0.0114</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.8886±0.0000</t>
+          <t>0.8950±0.0015</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.8985±0.0000</t>
+          <t>0.8979±0.0035</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.9146±0.0000</t>
+          <t>0.9105±0.0037</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9146±0.0000</t>
+          <t>0.9105±0.0037</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9146±0.0000</t>
+          <t>0.9105±0.0037</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8982±0.0000</t>
+          <t>0.8966±0.0011</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.7155±0.0000</t>
+          <t>0.8497±0.0028</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7921±0.0000</t>
+          <t>0.8956±0.0051</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.6208±0.0000</t>
+          <t>0.5438±0.0751</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.9539±0.0000</t>
+          <t>0.9506±0.0036</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5264±0.0000</t>
+          <t>0.6789±0.0110</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6159±0.0000</t>
+          <t>0.6703±0.0137</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.8453±0.0000</t>
+          <t>0.8296±0.0093</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8566±0.0060</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.9432±0.0000</t>
+          <t>0.9378±0.0080</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6698±0.0000</t>
+          <t>0.9313±0.0041</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6698±0.0000</t>
+          <t>0.9313±0.0041</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6698±0.0000</t>
+          <t>0.9313±0.0041</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.9326±0.0000</t>
+          <t>0.9290±0.0039</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6906±0.0000</t>
+          <t>0.8737±0.0048</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7713±0.0000</t>
+          <t>0.9265±0.0050</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7132±0.0000</t>
+          <t>0.7572±0.0081</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.8979±0.0000</t>
+          <t>0.8988±0.0027</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.5978±0.0000</t>
+          <t>0.7199±0.0329</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.6940±0.0000</t>
+          <t>0.7477±0.0139</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.8876±0.0000</t>
+          <t>0.8861±0.0040</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.8936±0.0000</t>
+          <t>0.8923±0.0014</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.8929±0.0000</t>
+          <t>0.9129±0.0036</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.9303±0.0000</t>
+          <t>0.9507±0.0019</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.9303±0.0000</t>
+          <t>0.9507±0.0019</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.9303±0.0000</t>
+          <t>0.9507±0.0019</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.8916±0.0000</t>
+          <t>0.9090±0.0013</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8735±0.0000</t>
+          <t>0.8898±0.0065</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.9071±0.0000</t>
+          <t>0.9362±0.0027</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.5912±0.0000</t>
+          <t>0.6583±0.0411</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.8947±0.0000</t>
+          <t>0.9277±0.0026</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4923±0.0000</t>
+          <t>0.7093±0.0119</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6060±0.0000</t>
+          <t>0.7086±0.0205</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.8767±0.0000</t>
+          <t>0.8916±0.0060</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.9112±0.0000</t>
+          <t>0.8898±0.0034</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8899±0.0000</t>
+          <t>0.9423±0.0018</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8893±0.0000</t>
+          <t>0.9464±0.0007</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8893±0.0000</t>
+          <t>0.9464±0.0007</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8893±0.0000</t>
+          <t>0.9464±0.0007</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8936±0.0000</t>
+          <t>0.9448±0.0013</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8471±0.0000</t>
+          <t>0.8498±0.0006</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8575±0.0000</t>
+          <t>0.9298±0.0020</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.5662±0.0000</t>
+          <t>0.6675±0.1113</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.9286±0.0000</t>
+          <t>0.9299±0.0009</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.6300±0.0000</t>
+          <t>0.6843±0.0126</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.7226±0.0000</t>
+          <t>0.7416±0.0119</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.8929±0.0000</t>
+          <t>0.9018±0.0110</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.8974±0.0000</t>
+          <t>0.9099±0.0130</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.9397±0.0000</t>
+          <t>0.9432±0.0025</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.9432±0.0000</t>
+          <t>0.9422±0.0011</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.9432±0.0000</t>
+          <t>0.9422±0.0011</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.9432±0.0000</t>
+          <t>0.9422±0.0011</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.9492±0.0000</t>
+          <t>0.9454±0.0027</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8828±0.0000</t>
+          <t>0.8784±0.0044</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.8953±0.0000</t>
+          <t>0.9020±0.0041</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.8265±0.0000</t>
+          <t>0.8180±0.0144</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.8962±0.0000</t>
+          <t>0.8993±0.0006</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6421±0.0000</t>
+          <t>0.7035±0.0062</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6823±0.0000</t>
+          <t>0.6962±0.0100</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.8890±0.0000</t>
+          <t>0.8884±0.0034</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.8951±0.0000</t>
+          <t>0.8905±0.0042</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.8992±0.0000</t>
+          <t>0.8989±0.0021</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.9120±0.0000</t>
+          <t>0.9118±0.0082</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.9120±0.0000</t>
+          <t>0.9128±0.0032</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.9120±0.0000</t>
+          <t>0.9126±0.0056</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.8997±0.0000</t>
+          <t>0.8962±0.0028</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.8848±0.0000</t>
+          <t>0.8909±0.0120</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.9118±0.0000</t>
+          <t>0.9151±0.0027</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.8145±0.0000</t>
+          <t>0.7741±0.0331</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.9160±0.0000</t>
+          <t>0.9095±0.0026</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4925±0.0000</t>
+          <t>0.7138±0.0187</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4911±0.0000</t>
+          <t>0.5750±0.0663</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.7741±0.0000</t>
+          <t>0.8775±0.0069</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.8746±0.0000</t>
+          <t>0.8765±0.0015</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.8266±0.0000</t>
+          <t>0.8612±0.0064</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7225±0.0000</t>
+          <t>0.7554±0.0033</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7225±0.0000</t>
+          <t>0.7554±0.0033</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7225±0.0000</t>
+          <t>0.7554±0.0033</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.8207±0.0000</t>
+          <t>0.8510±0.0048</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7505±0.0000</t>
+          <t>0.7745±0.0060</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6693±0.0000</t>
+          <t>0.7034±0.0043</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7649±0.0000</t>
+          <t>0.7216±0.0466</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8786±0.0000</t>
+          <t>0.8775±0.0020</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5629±0.0000</t>
+          <t>0.7594±0.0098</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7332±0.0000</t>
+          <t>0.7843±0.0363</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.8986±0.0000</t>
+          <t>0.8831±0.0115</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.8714±0.0000</t>
+          <t>0.8755±0.0024</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8788±0.0000</t>
+          <t>0.8754±0.0069</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.9064±0.0000</t>
+          <t>0.9026±0.0035</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9064±0.0000</t>
+          <t>0.9026±0.0035</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9064±0.0000</t>
+          <t>0.9026±0.0035</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8781±0.0000</t>
+          <t>0.8797±0.0050</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7468±0.0000</t>
+          <t>0.8279±0.0066</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7898±0.0000</t>
+          <t>0.8954±0.0025</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6915±0.0000</t>
+          <t>0.6384±0.0485</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.9469±0.0000</t>
+          <t>0.9419±0.0045</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5349±0.0000</t>
+          <t>0.7182±0.0040</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.6468±0.0000</t>
+          <t>0.7167±0.0088</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.8452±0.0000</t>
+          <t>0.8375±0.0066</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.8513±0.0045</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9401±0.0000</t>
+          <t>0.9361±0.0043</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7340±0.0000</t>
+          <t>0.9169±0.0066</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7340±0.0000</t>
+          <t>0.9169±0.0066</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7340±0.0000</t>
+          <t>0.9169±0.0066</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.9328±0.0000</t>
+          <t>0.9294±0.0027</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.6407±0.0000</t>
+          <t>0.8396±0.0036</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7960±0.0000</t>
+          <t>0.9123±0.0074</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.7131±0.0000</t>
+          <t>0.7438±0.0006</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.8736±0.0000</t>
+          <t>0.8752±0.0037</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6253±0.0000</t>
+          <t>0.7598±0.0133</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7276±0.0000</t>
+          <t>0.7826±0.0066</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.8710±0.0000</t>
+          <t>0.8705±0.0066</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.8760±0.0000</t>
+          <t>0.8756±0.0022</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.8776±0.0000</t>
+          <t>0.9059±0.0024</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.9324±0.0000</t>
+          <t>0.9530±0.0015</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.9324±0.0000</t>
+          <t>0.9530±0.0015</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.9324±0.0000</t>
+          <t>0.9530±0.0015</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8773±0.0000</t>
+          <t>0.9075±0.0056</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8640±0.0000</t>
+          <t>0.8800±0.0053</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.9010±0.0000</t>
+          <t>0.9352±0.0019</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.6505±0.0000</t>
+          <t>0.6937±0.0253</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8830±0.0000</t>
+          <t>0.9179±0.0029</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4961±0.0000</t>
+          <t>0.7636±0.0132</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5985±0.0000</t>
+          <t>0.7183±0.0423</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.8568±0.0000</t>
+          <t>0.8761±0.0078</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.9047±0.0000</t>
+          <t>0.8768±0.0031</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8965±0.0000</t>
+          <t>0.9448±0.0011</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8888±0.0000</t>
+          <t>0.9488±0.0003</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8888±0.0000</t>
+          <t>0.9488±0.0003</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8888±0.0000</t>
+          <t>0.9488±0.0003</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.9006±0.0000</t>
+          <t>0.9473±0.0010</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8376±0.0000</t>
+          <t>0.8383±0.0015</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8481±0.0000</t>
+          <t>0.9285±0.0008</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6519±0.0000</t>
+          <t>0.7024±0.0613</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.9167±0.0000</t>
+          <t>0.9180±0.0013</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6431±0.0000</t>
+          <t>0.7584±0.0025</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7652±0.0000</t>
+          <t>0.7736±0.0198</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.8779±0.0000</t>
+          <t>0.8884±0.0153</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.8848±0.0000</t>
+          <t>0.8958±0.0154</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.9287±0.0000</t>
+          <t>0.9327±0.0029</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.9354±0.0000</t>
+          <t>0.9353±0.0016</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.9354±0.0000</t>
+          <t>0.9353±0.0016</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.9354±0.0000</t>
+          <t>0.9353±0.0016</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.9399±0.0000</t>
+          <t>0.9357±0.0030</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8579±0.0000</t>
+          <t>0.8553±0.0037</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8958±0.0000</t>
+          <t>0.9042±0.0025</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7871±0.0000</t>
+          <t>0.7803±0.0126</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.8701±0.0000</t>
+          <t>0.8767±0.0025</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6718±0.0000</t>
+          <t>0.7434±0.0198</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7250±0.0000</t>
+          <t>0.7599±0.0247</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.8716±0.0000</t>
+          <t>0.8690±0.0037</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8715±0.0000</t>
+          <t>0.8711±0.0041</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.8780±0.0000</t>
+          <t>0.8768±0.0022</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.9008±0.0000</t>
+          <t>0.8986±0.0110</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.9008±0.0000</t>
+          <t>0.8980±0.0029</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.9008±0.0000</t>
+          <t>0.8980±0.0060</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8769±0.0000</t>
+          <t>0.8728±0.0032</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.8906±0.0000</t>
+          <t>0.8988±0.0114</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.8983±0.0000</t>
+          <t>0.9030±0.0039</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7776±0.0000</t>
+          <t>0.7492±0.0226</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.9009±0.0000</t>
+          <t>0.8915±0.0037</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4963±0.0000</t>
+          <t>0.7144±0.0190</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.4956±0.0000</t>
+          <t>0.5838±0.0668</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6936±0.0000</t>
+          <t>0.8643±0.0057</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.8636±0.0000</t>
+          <t>0.8655±0.0002</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.8196±0.0000</t>
+          <t>0.8544±0.0055</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7012±0.0000</t>
+          <t>0.7233±0.0029</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7012±0.0000</t>
+          <t>0.7233±0.0029</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7012±0.0000</t>
+          <t>0.7233±0.0029</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.8155±0.0000</t>
+          <t>0.8446±0.0030</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7230±0.0000</t>
+          <t>0.7469±0.0106</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6305±0.0000</t>
+          <t>0.6545±0.0046</t>
         </is>
       </c>
     </row>
